--- a/Ecobliss_Results.xlsx
+++ b/Ecobliss_Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2025/Ghana_Project/QA1_&amp;_3/Documentation/ecobliss-docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B38083A5-4097-3C47-A8E1-981044EB1424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A817B982-E94C-0144-B9FC-7E04CE45FE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{AA4B684E-F9E2-7F41-996C-BD2AB92E0EF7}"/>
+    <workbookView xWindow="-33760" yWindow="-9320" windowWidth="29400" windowHeight="18400" xr2:uid="{AA4B684E-F9E2-7F41-996C-BD2AB92E0EF7}"/>
   </bookViews>
   <sheets>
     <sheet name="Net ERs" sheetId="1" r:id="rId1"/>
@@ -2095,10 +2095,10 @@
       <c r="A5" t="s">
         <v>220</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -2139,18 +2139,18 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>12.2420891867305</v>
-      </c>
-      <c r="C6" s="1">
-        <v>4.27508219</v>
+        <v>36.879468944307497</v>
+      </c>
+      <c r="C6">
+        <v>28.9405112459125</v>
       </c>
       <c r="D6">
         <f>B6-C6</f>
-        <v>7.9670069967304995</v>
+        <v>7.9389576983949972</v>
       </c>
       <c r="F6" s="4">
         <f>D6*$B$2*44/12</f>
-        <v>531664.93358181533</v>
+        <v>529793.11040622613</v>
       </c>
       <c r="G6">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -2187,18 +2187,18 @@
         <v>2025</v>
       </c>
       <c r="B7">
-        <v>12.2420882231769</v>
-      </c>
-      <c r="C7" s="1">
-        <v>4.2750812099999997</v>
+        <v>36.8794679655715</v>
+      </c>
+      <c r="C7">
+        <v>28.9405102737269</v>
       </c>
       <c r="D7">
         <f t="shared" ref="D7:D18" si="0">B7-C7</f>
-        <v>7.9670070131769002</v>
+        <v>7.9389576918445997</v>
       </c>
       <c r="F7" s="4">
         <f t="shared" ref="F7:F18" si="1">D7*$B$2*44/12</f>
-        <v>531664.93467933836</v>
+        <v>529793.10996909626</v>
       </c>
       <c r="G7">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -2238,12 +2238,9 @@
         <f>SUM(L7,N7)</f>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7" s="123">
         <f>(W7+V7)*0.175</f>
-        <v>87461.965637465517</v>
+        <v>87134.396313173158</v>
       </c>
       <c r="V7">
         <f>R7-S7</f>
@@ -2251,11 +2248,11 @@
       </c>
       <c r="W7" s="123">
         <f>F7-G7</f>
-        <v>492585.17359529732</v>
+        <v>490713.34888505522</v>
       </c>
       <c r="X7" s="123">
         <f>W7+V7-U7</f>
-        <v>412320.69514805177</v>
+        <v>410776.43976210203</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.2">
@@ -2263,18 +2260,18 @@
         <v>2026</v>
       </c>
       <c r="B8">
-        <v>12.242087277836101</v>
-      </c>
-      <c r="C8" s="1">
-        <v>4.2750802500000002</v>
+        <v>36.879467005335201</v>
+      </c>
+      <c r="C8">
+        <v>29.334501623375701</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>7.9670070278361003</v>
+        <v>7.5449653819595</v>
       </c>
       <c r="F8" s="4">
         <f t="shared" si="1"/>
-        <v>531664.93565759575</v>
+        <v>503500.68982276396</v>
       </c>
       <c r="G8">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -2314,12 +2311,9 @@
         <f t="shared" ref="S8:S33" si="4">SUM(L8,N8)</f>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T8">
-        <v>1</v>
-      </c>
       <c r="U8" s="123">
         <f t="shared" ref="U8:U33" si="5">(W8+V8)*0.175</f>
-        <v>87461.965808660563</v>
+        <v>82533.222787564999</v>
       </c>
       <c r="V8">
         <f t="shared" ref="V8:V33" si="6">R8-S8</f>
@@ -2327,11 +2321,11 @@
       </c>
       <c r="W8" s="123">
         <f t="shared" ref="W8:W33" si="7">F8-G8</f>
-        <v>492585.17457355472</v>
+        <v>464420.92873872293</v>
       </c>
       <c r="X8" s="123">
         <f t="shared" ref="X8:X33" si="8">W8+V8-U8</f>
-        <v>412320.69595511415</v>
+        <v>389085.19314137788</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.2">
@@ -2339,18 +2333,18 @@
         <v>2027</v>
       </c>
       <c r="B9">
-        <v>12.242086350363801</v>
-      </c>
-      <c r="C9" s="1">
-        <v>4.2750793099999997</v>
+        <v>36.879466063248998</v>
+      </c>
+      <c r="C9">
+        <v>28.961326793124901</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>7.9670070403638009</v>
+        <v>7.9181392701240974</v>
       </c>
       <c r="F9" s="4">
         <f t="shared" si="1"/>
-        <v>531664.93649361108</v>
+        <v>528403.82729294803</v>
       </c>
       <c r="G9">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -2390,12 +2384,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T9">
-        <v>2</v>
-      </c>
       <c r="U9" s="123">
         <f t="shared" si="5"/>
-        <v>87461.965954963249</v>
+        <v>86891.271844847215</v>
       </c>
       <c r="V9">
         <f t="shared" si="6"/>
@@ -2403,11 +2394,11 @@
       </c>
       <c r="W9" s="123">
         <f t="shared" si="7"/>
-        <v>492585.17540957005</v>
+        <v>489324.066208907</v>
       </c>
       <c r="X9" s="123">
         <f t="shared" si="8"/>
-        <v>412320.69664482679</v>
+        <v>409630.28155427973</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.2">
@@ -2415,18 +2406,18 @@
         <v>2028</v>
       </c>
       <c r="B10">
-        <v>12.242085440422301</v>
-      </c>
-      <c r="C10" s="1">
-        <v>4.27507839</v>
+        <v>36.879465138969799</v>
+      </c>
+      <c r="C10">
+        <v>28.955400076170299</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>7.9670070504223007</v>
+        <v>7.9240650627994995</v>
       </c>
       <c r="F10" s="4">
         <f t="shared" si="1"/>
-        <v>531664.9371648482</v>
+        <v>528799.27519081987</v>
       </c>
       <c r="G10">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -2466,12 +2457,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T10">
-        <v>3</v>
-      </c>
       <c r="U10" s="123">
         <f t="shared" si="5"/>
-        <v>87461.966072429743</v>
+        <v>86960.475226974784</v>
       </c>
       <c r="V10">
         <f t="shared" si="6"/>
@@ -2479,11 +2467,11 @@
       </c>
       <c r="W10" s="123">
         <f t="shared" si="7"/>
-        <v>492585.17608080717</v>
+        <v>489719.51410677884</v>
       </c>
       <c r="X10" s="123">
         <f t="shared" si="8"/>
-        <v>412320.69719859742</v>
+        <v>409956.526070024</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.2">
@@ -2491,18 +2479,18 @@
         <v>2029</v>
       </c>
       <c r="B11">
-        <v>12.2420845476803</v>
-      </c>
-      <c r="C11" s="1">
-        <v>4.2750774900000001</v>
+        <v>36.879464232160998</v>
+      </c>
+      <c r="C11">
+        <v>28.951245560448001</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>7.9670070576802994</v>
+        <v>7.9282186717129974</v>
       </c>
       <c r="F11" s="4">
         <f t="shared" si="1"/>
-        <v>531664.93764919869</v>
+        <v>529076.45935898076</v>
       </c>
       <c r="G11">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -2542,12 +2530,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T11">
-        <v>4</v>
-      </c>
       <c r="U11" s="123">
         <f t="shared" si="5"/>
-        <v>87461.966157191084</v>
+        <v>87008.98245640294</v>
       </c>
       <c r="V11">
         <f t="shared" si="6"/>
@@ -2555,11 +2540,11 @@
       </c>
       <c r="W11" s="123">
         <f t="shared" si="7"/>
-        <v>492585.17656515766</v>
+        <v>489996.69827493973</v>
       </c>
       <c r="X11" s="123">
         <f t="shared" si="8"/>
-        <v>412320.69759818655</v>
+        <v>410185.20300875674</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.2">
@@ -2567,18 +2552,18 @@
         <v>2030</v>
       </c>
       <c r="B12">
-        <v>12.2420836718125</v>
-      </c>
-      <c r="C12" s="1">
-        <v>4.2750766000000002</v>
+        <v>36.8794633424925</v>
+      </c>
+      <c r="C12">
+        <v>28.948308913353099</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>7.9670070718124997</v>
+        <v>7.9311544291394007</v>
       </c>
       <c r="F12" s="4">
         <f t="shared" si="1"/>
-        <v>531664.9385922876</v>
+        <v>529272.37223790272</v>
       </c>
       <c r="G12">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -2618,12 +2603,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T12">
-        <v>5</v>
-      </c>
       <c r="U12" s="123">
         <f t="shared" si="5"/>
-        <v>87461.966322231645</v>
+        <v>87043.267210214282</v>
       </c>
       <c r="V12">
         <f t="shared" si="6"/>
@@ -2631,11 +2613,11 @@
       </c>
       <c r="W12" s="123">
         <f t="shared" si="7"/>
-        <v>492585.17750824656</v>
+        <v>490192.61115386168</v>
       </c>
       <c r="X12" s="123">
         <f t="shared" si="8"/>
-        <v>412320.69837623491</v>
+        <v>410346.83113386738</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.2">
@@ -2643,18 +2625,18 @@
         <v>2031</v>
       </c>
       <c r="B13">
-        <v>12.242082812500101</v>
-      </c>
-      <c r="C13" s="1">
-        <v>4.2750757300000002</v>
+        <v>36.879462469640103</v>
+      </c>
+      <c r="C13">
+        <v>28.946221403616299</v>
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>7.9670070825001007</v>
+        <v>7.933241066023804</v>
       </c>
       <c r="F13" s="4">
         <f t="shared" si="1"/>
-        <v>531664.93930550665</v>
+        <v>529411.62047265517</v>
       </c>
       <c r="G13">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -2694,12 +2676,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T13">
-        <v>6</v>
-      </c>
       <c r="U13" s="123">
         <f t="shared" si="5"/>
-        <v>87461.966447044979</v>
+        <v>87067.635651295961</v>
       </c>
       <c r="V13">
         <f t="shared" si="6"/>
@@ -2707,11 +2686,11 @@
       </c>
       <c r="W13" s="123">
         <f t="shared" si="7"/>
-        <v>492585.17822146561</v>
+        <v>490331.85938861413</v>
       </c>
       <c r="X13" s="123">
         <f t="shared" si="8"/>
-        <v>412320.69896464061</v>
+        <v>410461.71092753817</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.2">
@@ -2719,18 +2698,18 @@
         <v>2032</v>
       </c>
       <c r="B14">
-        <v>12.242081969430201</v>
-      </c>
-      <c r="C14" s="1">
-        <v>4.2750748700000001</v>
+        <v>36.879461613286097</v>
+      </c>
+      <c r="C14">
+        <v>28.944730915749201</v>
       </c>
       <c r="D14">
         <f t="shared" si="0"/>
-        <v>7.9670070994302007</v>
+        <v>7.9347306975368959</v>
       </c>
       <c r="F14" s="4">
         <f t="shared" si="1"/>
-        <v>531664.94043530873</v>
+        <v>529511.0285489622</v>
       </c>
       <c r="G14">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -2770,12 +2749,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T14">
-        <v>7</v>
-      </c>
       <c r="U14" s="123">
         <f t="shared" si="5"/>
-        <v>87461.966644760338</v>
+        <v>87085.032064649698</v>
       </c>
       <c r="V14">
         <f t="shared" si="6"/>
@@ -2783,11 +2759,11 @@
       </c>
       <c r="W14" s="123">
         <f t="shared" si="7"/>
-        <v>492585.1793512677</v>
+        <v>490431.26746492117</v>
       </c>
       <c r="X14" s="123">
         <f t="shared" si="8"/>
-        <v>412320.69989672734</v>
+        <v>410543.72259049147</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.2">
@@ -2795,18 +2771,18 @@
         <v>2033</v>
       </c>
       <c r="B15">
-        <v>12.2420811422956</v>
-      </c>
-      <c r="C15" s="1">
-        <v>4.2750740399999998</v>
+        <v>36.879460773118701</v>
+      </c>
+      <c r="C15">
+        <v>28.943662883495399</v>
       </c>
       <c r="D15">
         <f t="shared" si="0"/>
-        <v>7.9670071022956002</v>
+        <v>7.9357978896233021</v>
       </c>
       <c r="F15" s="4">
         <f t="shared" si="1"/>
-        <v>531664.94062652637</v>
+        <v>529582.24583419494</v>
       </c>
       <c r="G15">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -2846,12 +2822,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T15">
-        <v>8</v>
-      </c>
       <c r="U15" s="123">
         <f t="shared" si="5"/>
-        <v>87461.966678223427</v>
+        <v>87097.495089565418</v>
       </c>
       <c r="V15">
         <f t="shared" si="6"/>
@@ -2859,11 +2832,11 @@
       </c>
       <c r="W15" s="123">
         <f t="shared" si="7"/>
-        <v>492585.17954248533</v>
+        <v>490502.4847501539</v>
       </c>
       <c r="X15" s="123">
         <f t="shared" si="8"/>
-        <v>412320.70005448186</v>
+        <v>410602.47685080848</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.2">
@@ -2871,18 +2844,18 @@
         <v>2034</v>
       </c>
       <c r="B16">
-        <v>12.2420803307953</v>
-      </c>
-      <c r="C16" s="1">
-        <v>4.2750732100000004</v>
+        <v>36.879459948831801</v>
+      </c>
+      <c r="C16">
+        <v>28.9428952323752</v>
       </c>
       <c r="D16">
         <f t="shared" si="0"/>
-        <v>7.9670071207952997</v>
+        <v>7.9365647164566013</v>
       </c>
       <c r="F16" s="4">
         <f t="shared" si="1"/>
-        <v>531664.9418610729</v>
+        <v>529633.41874487046</v>
       </c>
       <c r="G16">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -2922,12 +2895,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T16">
-        <v>9</v>
-      </c>
       <c r="U16" s="123">
         <f t="shared" si="5"/>
-        <v>87461.966894269062</v>
+        <v>87106.450348933635</v>
       </c>
       <c r="V16">
         <f t="shared" si="6"/>
@@ -2935,11 +2905,11 @@
       </c>
       <c r="W16" s="123">
         <f t="shared" si="7"/>
-        <v>492585.18077703187</v>
+        <v>490553.65766082943</v>
       </c>
       <c r="X16" s="123">
         <f t="shared" si="8"/>
-        <v>412320.7010729828</v>
+        <v>410644.69450211577</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.2">
@@ -2947,18 +2917,18 @@
         <v>2035</v>
       </c>
       <c r="B17">
-        <v>12.242079534633699</v>
-      </c>
-      <c r="C17" s="1">
-        <v>4.2750724099999999</v>
+        <v>36.879459140125299</v>
+      </c>
+      <c r="C17">
+        <v>28.942341940656998</v>
       </c>
       <c r="D17">
         <f t="shared" si="0"/>
-        <v>7.9670071246336995</v>
+        <v>7.9371171994683003</v>
       </c>
       <c r="F17" s="4">
         <f t="shared" si="1"/>
-        <v>531664.94211722224</v>
+        <v>529670.28777785122</v>
       </c>
       <c r="G17">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -2998,12 +2968,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T17">
-        <v>10</v>
-      </c>
       <c r="U17" s="123">
         <f t="shared" si="5"/>
-        <v>87461.966939095204</v>
+        <v>87112.902429705267</v>
       </c>
       <c r="V17">
         <f t="shared" si="6"/>
@@ -3011,11 +2978,11 @@
       </c>
       <c r="W17" s="123">
         <f t="shared" si="7"/>
-        <v>492585.1810331812</v>
+        <v>490590.52669381018</v>
       </c>
       <c r="X17" s="123">
         <f t="shared" si="8"/>
-        <v>412320.70128430601</v>
+        <v>410675.11145432491</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.2">
@@ -3023,18 +2990,18 @@
         <v>2036</v>
       </c>
       <c r="B18">
-        <v>12.242078753521</v>
-      </c>
-      <c r="C18" s="1">
-        <v>4.2750716200000003</v>
+        <v>36.879458346704702</v>
+      </c>
+      <c r="C18">
+        <v>28.941942038985399</v>
       </c>
       <c r="D18">
         <f t="shared" si="0"/>
-        <v>7.9670071335209993</v>
+        <v>7.9375163077193029</v>
       </c>
       <c r="F18" s="4">
         <f t="shared" si="1"/>
-        <v>531664.94271030126</v>
+        <v>529696.92160180153</v>
       </c>
       <c r="G18">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3074,12 +3041,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T18">
-        <v>11</v>
-      </c>
       <c r="U18" s="123">
         <f t="shared" si="5"/>
-        <v>87461.967042884033</v>
+        <v>87117.563348896583</v>
       </c>
       <c r="V18">
         <f t="shared" si="6"/>
@@ -3087,11 +3051,11 @@
       </c>
       <c r="W18" s="123">
         <f t="shared" si="7"/>
-        <v>492585.18162626022</v>
+        <v>490617.16051776049</v>
       </c>
       <c r="X18" s="123">
         <f t="shared" si="8"/>
-        <v>412320.70177359617</v>
+        <v>410697.08435908391</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.2">
@@ -3099,18 +3063,18 @@
         <v>2037</v>
       </c>
       <c r="B19">
-        <v>12.2420779871725</v>
-      </c>
-      <c r="C19" s="1">
-        <v>4.2750708399999997</v>
+        <v>36.879457568281097</v>
+      </c>
+      <c r="C19">
+        <v>28.9416521256558</v>
       </c>
       <c r="D19">
         <f t="shared" ref="D19:D47" si="9">B19-C19</f>
-        <v>7.9670071471725006</v>
+        <v>7.9378054426252973</v>
       </c>
       <c r="F19" s="4">
         <f t="shared" ref="F19:F47" si="10">D19*$B$2*44/12</f>
-        <v>531664.94362131145</v>
+        <v>529716.2165378615</v>
       </c>
       <c r="G19">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3150,12 +3114,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T19">
-        <v>12</v>
-      </c>
       <c r="U19" s="123">
         <f t="shared" si="5"/>
-        <v>87461.967202310814</v>
+        <v>87120.939962707067</v>
       </c>
       <c r="V19">
         <f t="shared" si="6"/>
@@ -3163,11 +3124,11 @@
       </c>
       <c r="W19" s="123">
         <f t="shared" si="7"/>
-        <v>492585.18253727042</v>
+        <v>490636.45545382047</v>
       </c>
       <c r="X19" s="123">
         <f t="shared" si="8"/>
-        <v>412320.7025251796</v>
+        <v>410713.0026813334</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.2">
@@ -3175,18 +3136,18 @@
         <v>2038</v>
       </c>
       <c r="B20">
-        <v>12.242077235309299</v>
-      </c>
-      <c r="C20" s="1">
-        <v>4.2750700799999999</v>
+        <v>36.879456804570999</v>
+      </c>
+      <c r="C20">
+        <v>28.941441204343501</v>
       </c>
       <c r="D20">
         <f t="shared" si="9"/>
-        <v>7.9670071553092994</v>
+        <v>7.938015600227498</v>
       </c>
       <c r="F20" s="4">
         <f t="shared" si="10"/>
-        <v>531664.94416430721</v>
+        <v>529730.2410551816</v>
       </c>
       <c r="G20">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3226,12 +3187,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T20">
-        <v>13</v>
-      </c>
       <c r="U20" s="123">
         <f t="shared" si="5"/>
-        <v>87461.967297335068</v>
+        <v>87123.39425323809</v>
       </c>
       <c r="V20">
         <f t="shared" si="6"/>
@@ -3239,11 +3197,11 @@
       </c>
       <c r="W20" s="123">
         <f t="shared" si="7"/>
-        <v>492585.18308026617</v>
+        <v>490650.47997114056</v>
       </c>
       <c r="X20" s="123">
         <f t="shared" si="8"/>
-        <v>412320.70297315111</v>
+        <v>410724.57290812244</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.2">
@@ -3251,18 +3209,18 @@
         <v>2039</v>
       </c>
       <c r="B21">
-        <v>12.2420764976576</v>
-      </c>
-      <c r="C21" s="1">
-        <v>4.27506933</v>
+        <v>36.879456055296302</v>
+      </c>
+      <c r="C21">
+        <v>28.941287085116201</v>
       </c>
       <c r="D21">
         <f t="shared" si="9"/>
-        <v>7.9670071676575995</v>
+        <v>7.9381689701801008</v>
       </c>
       <c r="F21" s="4">
         <f t="shared" si="10"/>
-        <v>531664.9449883505</v>
+        <v>529740.47594335198</v>
       </c>
       <c r="G21">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3302,12 +3260,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T21">
-        <v>14</v>
-      </c>
       <c r="U21" s="123">
         <f t="shared" si="5"/>
-        <v>87461.967441542642</v>
+        <v>87125.185358667906</v>
       </c>
       <c r="V21">
         <f t="shared" si="6"/>
@@ -3315,11 +3270,11 @@
       </c>
       <c r="W21" s="123">
         <f t="shared" si="7"/>
-        <v>492585.18390430947</v>
+        <v>490660.71485931095</v>
       </c>
       <c r="X21" s="123">
         <f t="shared" si="8"/>
-        <v>412320.70365298679</v>
+        <v>410733.01669086301</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.2">
@@ -3327,18 +3282,18 @@
         <v>2040</v>
       </c>
       <c r="B22">
-        <v>12.242075773948701</v>
-      </c>
-      <c r="C22" s="1">
-        <v>4.2750686</v>
+        <v>36.8794553201841</v>
+      </c>
+      <c r="C22">
+        <v>28.941173854285498</v>
       </c>
       <c r="D22">
         <f t="shared" si="9"/>
-        <v>7.9670071739487005</v>
+        <v>7.9382814658986014</v>
       </c>
       <c r="F22" s="4">
         <f t="shared" si="10"/>
-        <v>531664.94540817663</v>
+        <v>529747.98315763334</v>
       </c>
       <c r="G22">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3378,12 +3333,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T22">
-        <v>15</v>
-      </c>
       <c r="U22" s="123">
         <f t="shared" si="5"/>
-        <v>87461.96751501222</v>
+        <v>87126.499121167144</v>
       </c>
       <c r="V22">
         <f t="shared" si="6"/>
@@ -3391,11 +3343,11 @@
       </c>
       <c r="W22" s="123">
         <f t="shared" si="7"/>
-        <v>492585.1843241356</v>
+        <v>490668.2220735923</v>
       </c>
       <c r="X22" s="123">
         <f t="shared" si="8"/>
-        <v>412320.70399934333</v>
+        <v>410739.21014264517</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.2">
@@ -3403,18 +3355,18 @@
         <v>2041</v>
       </c>
       <c r="B23">
-        <v>12.2420750639192</v>
-      </c>
-      <c r="C23" s="1">
-        <v>4.2750678799999999</v>
+        <v>36.879454598966802</v>
+      </c>
+      <c r="C23">
+        <v>28.9410900843063</v>
       </c>
       <c r="D23">
         <f t="shared" si="9"/>
-        <v>7.9670071839192005</v>
+        <v>7.9383645146605026</v>
       </c>
       <c r="F23" s="4">
         <f t="shared" si="10"/>
-        <v>531664.9460735413</v>
+        <v>529753.52527834417</v>
       </c>
       <c r="G23">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3454,12 +3406,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T23">
-        <v>16</v>
-      </c>
       <c r="U23" s="123">
         <f t="shared" si="5"/>
-        <v>87461.967631451043</v>
+        <v>87127.468992291542</v>
       </c>
       <c r="V23">
         <f t="shared" si="6"/>
@@ -3467,11 +3416,11 @@
       </c>
       <c r="W23" s="123">
         <f t="shared" si="7"/>
-        <v>492585.18498950027</v>
+        <v>490673.76419430313</v>
       </c>
       <c r="X23" s="123">
         <f t="shared" si="8"/>
-        <v>412320.70454826922</v>
+        <v>410743.78239223157</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.2">
@@ -3479,18 +3428,18 @@
         <v>2042</v>
       </c>
       <c r="B24">
-        <v>12.2420743673104</v>
-      </c>
-      <c r="C24" s="1">
-        <v>4.2750671699999998</v>
+        <v>36.879453891381701</v>
+      </c>
+      <c r="C24">
+        <v>28.9410275611773</v>
       </c>
       <c r="D24">
         <f t="shared" si="9"/>
-        <v>7.9670071973103997</v>
+        <v>7.9384263302044005</v>
       </c>
       <c r="F24" s="4">
         <f t="shared" si="10"/>
-        <v>531664.9469671807</v>
+        <v>529757.65043564024</v>
       </c>
       <c r="G24">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3530,12 +3479,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T24">
-        <v>17</v>
-      </c>
       <c r="U24" s="123">
         <f t="shared" si="5"/>
-        <v>87461.96778783793</v>
+        <v>87128.190894818355</v>
       </c>
       <c r="V24">
         <f t="shared" si="6"/>
@@ -3543,11 +3489,11 @@
       </c>
       <c r="W24" s="123">
         <f t="shared" si="7"/>
-        <v>492585.18588313967</v>
+        <v>490677.88935159921</v>
       </c>
       <c r="X24" s="123">
         <f t="shared" si="8"/>
-        <v>412320.70528552169</v>
+        <v>410747.18564700085</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.2">
@@ -3555,18 +3501,18 @@
         <v>2043</v>
       </c>
       <c r="B25">
-        <v>12.2420736838686</v>
-      </c>
-      <c r="C25" s="1">
-        <v>4.2750664799999996</v>
+        <v>36.879453197171102</v>
+      </c>
+      <c r="C25">
+        <v>28.9409803764987</v>
       </c>
       <c r="D25">
         <f t="shared" si="9"/>
-        <v>7.9670072038686008</v>
+        <v>7.938472820672402</v>
       </c>
       <c r="F25" s="4">
         <f t="shared" si="10"/>
-        <v>531664.9474048313</v>
+        <v>529760.75289953826</v>
       </c>
       <c r="G25">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3606,12 +3552,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T25">
-        <v>18</v>
-      </c>
       <c r="U25" s="123">
         <f t="shared" si="5"/>
-        <v>87461.967864426784</v>
+        <v>87128.733826000505</v>
       </c>
       <c r="V25">
         <f t="shared" si="6"/>
@@ -3619,11 +3562,11 @@
       </c>
       <c r="W25" s="123">
         <f t="shared" si="7"/>
-        <v>492585.18632079026</v>
+        <v>490680.99181549723</v>
       </c>
       <c r="X25" s="123">
         <f t="shared" si="8"/>
-        <v>412320.70564658346</v>
+        <v>410749.74517971673</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.2">
@@ -3631,18 +3574,18 @@
         <v>2044</v>
       </c>
       <c r="B26">
-        <v>12.242073013345101</v>
-      </c>
-      <c r="C26" s="1">
-        <v>4.2750658000000001</v>
+        <v>36.879452516082303</v>
+      </c>
+      <c r="C26">
+        <v>28.9409442779796</v>
       </c>
       <c r="D26">
         <f t="shared" si="9"/>
-        <v>7.9670072133451004</v>
+        <v>7.9385082381027026</v>
       </c>
       <c r="F26" s="4">
         <f t="shared" si="10"/>
-        <v>531664.94803722971</v>
+        <v>529763.11642272037</v>
       </c>
       <c r="G26">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3682,12 +3625,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T26">
-        <v>19</v>
-      </c>
       <c r="U26" s="123">
         <f t="shared" si="5"/>
-        <v>87461.967975096515</v>
+        <v>87129.147442557369</v>
       </c>
       <c r="V26">
         <f t="shared" si="6"/>
@@ -3695,11 +3635,11 @@
       </c>
       <c r="W26" s="123">
         <f t="shared" si="7"/>
-        <v>492585.18695318868</v>
+        <v>490683.35533867934</v>
       </c>
       <c r="X26" s="123">
         <f t="shared" si="8"/>
-        <v>412320.70616831211</v>
+        <v>410751.69508634193</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.2">
@@ -3707,18 +3647,18 @@
         <v>2045</v>
       </c>
       <c r="B27">
-        <v>12.2420723554955</v>
-      </c>
-      <c r="C27" s="1">
-        <v>4.2750651299999998</v>
+        <v>36.879451847867202</v>
+      </c>
+      <c r="C27">
+        <v>28.940916203919301</v>
       </c>
       <c r="D27">
         <f t="shared" si="9"/>
-        <v>7.9670072254955002</v>
+        <v>7.9385356439479011</v>
       </c>
       <c r="F27" s="4">
         <f t="shared" si="10"/>
-        <v>531664.94884806639</v>
+        <v>529764.94530612335</v>
       </c>
       <c r="G27">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3758,12 +3698,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T27">
-        <v>20</v>
-      </c>
       <c r="U27" s="123">
         <f t="shared" si="5"/>
-        <v>87461.968116992924</v>
+        <v>87129.467497152902</v>
       </c>
       <c r="V27">
         <f t="shared" si="6"/>
@@ -3771,11 +3708,11 @@
       </c>
       <c r="W27" s="123">
         <f t="shared" si="7"/>
-        <v>492585.18776402535</v>
+        <v>490685.18422208232</v>
       </c>
       <c r="X27" s="123">
         <f t="shared" si="8"/>
-        <v>412320.70683725242</v>
+        <v>410753.20391514938</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.2">
@@ -3783,18 +3720,18 @@
         <v>2046</v>
       </c>
       <c r="B28">
-        <v>12.2420717100805</v>
-      </c>
-      <c r="C28" s="1">
-        <v>4.2750644800000002</v>
+        <v>36.879451192282502</v>
+      </c>
+      <c r="C28">
+        <v>28.940893949074798</v>
       </c>
       <c r="D28">
         <f t="shared" si="9"/>
-        <v>7.9670072300805002</v>
+        <v>7.9385572432077041</v>
       </c>
       <c r="F28" s="4">
         <f t="shared" si="10"/>
-        <v>531664.9491540388</v>
+        <v>529766.38669672748</v>
       </c>
       <c r="G28">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3834,12 +3771,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T28">
-        <v>21</v>
-      </c>
       <c r="U28" s="123">
         <f t="shared" si="5"/>
-        <v>87461.968170538094</v>
+        <v>87129.719740508619</v>
       </c>
       <c r="V28">
         <f t="shared" si="6"/>
@@ -3847,11 +3781,11 @@
       </c>
       <c r="W28" s="123">
         <f t="shared" si="7"/>
-        <v>492585.18806999776</v>
+        <v>490686.62561268645</v>
       </c>
       <c r="X28" s="123">
         <f t="shared" si="8"/>
-        <v>412320.70708967966</v>
+        <v>410754.39306239784</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.2">
@@ -3859,18 +3793,18 @@
         <v>2047</v>
       </c>
       <c r="B29">
-        <v>12.2420710768648</v>
-      </c>
-      <c r="C29" s="1">
-        <v>4.2750638399999996</v>
+        <v>36.879450549089498</v>
+      </c>
+      <c r="C29">
+        <v>28.940875924581</v>
       </c>
       <c r="D29">
         <f t="shared" si="9"/>
-        <v>7.9670072368648004</v>
+        <v>7.9385746245084974</v>
       </c>
       <c r="F29" s="4">
         <f t="shared" si="10"/>
-        <v>531664.94960677763</v>
+        <v>529767.54660886712</v>
       </c>
       <c r="G29">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3910,12 +3844,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T29">
-        <v>22</v>
-      </c>
       <c r="U29" s="123">
         <f t="shared" si="5"/>
-        <v>87461.968249767393</v>
+        <v>87129.922725133059</v>
       </c>
       <c r="V29">
         <f t="shared" si="6"/>
@@ -3923,11 +3854,11 @@
       </c>
       <c r="W29" s="123">
         <f t="shared" si="7"/>
-        <v>492585.1885227366</v>
+        <v>490687.78552482609</v>
       </c>
       <c r="X29" s="123">
         <f t="shared" si="8"/>
-        <v>412320.7074631892</v>
+        <v>410755.349989913</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.2">
@@ -3935,18 +3866,18 @@
         <v>2048</v>
       </c>
       <c r="B30">
-        <v>12.242070455618</v>
-      </c>
-      <c r="C30" s="1">
-        <v>4.2750632099999999</v>
+        <v>36.879449918053801</v>
+      </c>
+      <c r="C30">
+        <v>28.9408609853174</v>
       </c>
       <c r="D30">
         <f t="shared" si="9"/>
-        <v>7.9670072456180003</v>
+        <v>7.9385889327364012</v>
       </c>
       <c r="F30" s="4">
         <f t="shared" si="10"/>
-        <v>531664.95019090781</v>
+        <v>529768.50144460914</v>
       </c>
       <c r="G30">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -3986,12 +3917,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T30">
-        <v>23</v>
-      </c>
       <c r="U30" s="123">
         <f t="shared" si="5"/>
-        <v>87461.968351990174</v>
+        <v>87130.089821387912</v>
       </c>
       <c r="V30">
         <f t="shared" si="6"/>
@@ -3999,11 +3927,11 @@
       </c>
       <c r="W30" s="123">
         <f t="shared" si="7"/>
-        <v>492585.18910686678</v>
+        <v>490688.7403605681</v>
       </c>
       <c r="X30" s="123">
         <f t="shared" si="8"/>
-        <v>412320.7079450966</v>
+        <v>410756.13772940019</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.2">
@@ -4011,18 +3939,18 @@
         <v>2049</v>
       </c>
       <c r="B31">
-        <v>12.2420698461138</v>
-      </c>
-      <c r="C31" s="1">
-        <v>4.2750625900000001</v>
+        <v>36.879449298945801</v>
+      </c>
+      <c r="C31">
+        <v>28.940848305705799</v>
       </c>
       <c r="D31">
         <f t="shared" si="9"/>
-        <v>7.9670072561138001</v>
+        <v>7.9386009932400015</v>
       </c>
       <c r="F31" s="4">
         <f t="shared" si="10"/>
-        <v>531664.95089132758</v>
+        <v>529769.3062822161</v>
       </c>
       <c r="G31">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4062,12 +3990,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T31">
-        <v>24</v>
-      </c>
       <c r="U31" s="123">
         <f t="shared" si="5"/>
-        <v>87461.968474563633</v>
+        <v>87130.230667969125</v>
       </c>
       <c r="V31">
         <f t="shared" si="6"/>
@@ -4075,11 +4000,11 @@
       </c>
       <c r="W31" s="123">
         <f t="shared" si="7"/>
-        <v>492585.18980728654</v>
+        <v>490689.54519817507</v>
       </c>
       <c r="X31" s="123">
         <f t="shared" si="8"/>
-        <v>412320.70852294291</v>
+        <v>410756.80172042595</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.2">
@@ -4087,18 +4012,18 @@
         <v>2050</v>
       </c>
       <c r="B32">
-        <v>12.2420692481302</v>
-      </c>
-      <c r="C32" s="1">
-        <v>4.2750619800000003</v>
+        <v>36.879448691539999</v>
+      </c>
+      <c r="C32">
+        <v>28.940837290314001</v>
       </c>
       <c r="D32">
         <f t="shared" si="9"/>
-        <v>7.9670072681301995</v>
+        <v>7.9386114012259981</v>
       </c>
       <c r="F32" s="4">
         <f t="shared" si="10"/>
-        <v>531664.95169322204</v>
+        <v>529770.00084181491</v>
       </c>
       <c r="G32">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4138,12 +4063,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T32">
-        <v>25</v>
-      </c>
       <c r="U32" s="123">
         <f t="shared" si="5"/>
-        <v>87461.968614895173</v>
+        <v>87130.352215898922</v>
       </c>
       <c r="V32">
         <f t="shared" si="6"/>
@@ -4151,11 +4073,11 @@
       </c>
       <c r="W32" s="123">
         <f t="shared" si="7"/>
-        <v>492585.19060918101</v>
+        <v>490690.23975777387</v>
       </c>
       <c r="X32" s="123">
         <f t="shared" si="8"/>
-        <v>412320.7091845058</v>
+        <v>410757.37473209493</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.2">
@@ -4163,18 +4085,18 @@
         <v>2051</v>
       </c>
       <c r="B33">
-        <v>12.242068661449601</v>
-      </c>
-      <c r="C33" s="1">
-        <v>4.2750613900000003</v>
+        <v>36.879448095615203</v>
+      </c>
+      <c r="C33">
+        <v>28.940827509494401</v>
       </c>
       <c r="D33">
         <f t="shared" si="9"/>
-        <v>7.9670072714496003</v>
+        <v>7.9386205861208019</v>
       </c>
       <c r="F33" s="4">
         <f t="shared" si="10"/>
-        <v>531664.95191473665</v>
+        <v>529770.61378046148</v>
       </c>
       <c r="G33">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4214,12 +4136,9 @@
         <f t="shared" si="4"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T33">
-        <v>26</v>
-      </c>
       <c r="U33" s="123">
         <f t="shared" si="5"/>
-        <v>87461.968653660224</v>
+        <v>87130.45948016207</v>
       </c>
       <c r="V33">
         <f t="shared" si="6"/>
@@ -4227,11 +4146,11 @@
       </c>
       <c r="W33" s="123">
         <f t="shared" si="7"/>
-        <v>492585.19083069562</v>
+        <v>490690.85269642045</v>
       </c>
       <c r="X33" s="123">
         <f t="shared" si="8"/>
-        <v>412320.70936725539</v>
+        <v>410757.88040647836</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.2">
@@ -4239,18 +4158,18 @@
         <v>2052</v>
       </c>
       <c r="B34">
-        <v>12.242068085858101</v>
-      </c>
-      <c r="C34" s="1">
-        <v>4.2750608100000003</v>
+        <v>36.8794475109543</v>
+      </c>
+      <c r="C34">
+        <v>28.940818653034999</v>
       </c>
       <c r="D34">
         <f t="shared" si="9"/>
-        <v>7.9670072758581005</v>
+        <v>7.9386288579193014</v>
       </c>
       <c r="F34" s="4">
         <f t="shared" si="10"/>
-        <v>531664.95220893063</v>
+        <v>529771.16578514816</v>
       </c>
       <c r="G34">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4290,12 +4209,9 @@
         <f>SUM(L34,N34)</f>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T34">
-        <v>27</v>
-      </c>
       <c r="U34" s="123">
         <f>(W34+V34)*0.175</f>
-        <v>87461.968705144172</v>
+        <v>87130.556080982235</v>
       </c>
       <c r="V34">
         <f>R34-S34</f>
@@ -4303,11 +4219,11 @@
       </c>
       <c r="W34" s="123">
         <f>F34-G34</f>
-        <v>492585.19112488959</v>
+        <v>490691.40470110712</v>
       </c>
       <c r="X34" s="123">
         <f>W34+V34-U34</f>
-        <v>412320.70960996539</v>
+        <v>410758.3358103449</v>
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.2">
@@ -4315,18 +4231,18 @@
         <v>2053</v>
       </c>
       <c r="B35">
-        <v>12.242067521146399</v>
-      </c>
-      <c r="C35" s="1">
-        <v>4.2750602300000002</v>
+        <v>36.879446937344497</v>
+      </c>
+      <c r="C35">
+        <v>28.940810496778301</v>
       </c>
       <c r="D35">
         <f t="shared" si="9"/>
-        <v>7.9670072911463992</v>
+        <v>7.9386364405661958</v>
       </c>
       <c r="F35" s="4">
         <f t="shared" si="10"/>
-        <v>531664.95322916971</v>
+        <v>529771.67180045077</v>
       </c>
       <c r="G35">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4366,12 +4282,9 @@
         <f t="shared" ref="S35:S47" si="13">SUM(L35,N35)</f>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T35">
-        <v>28</v>
-      </c>
       <c r="U35" s="123">
         <f t="shared" ref="U35:U47" si="14">(W35+V35)*0.175</f>
-        <v>87461.968883686015</v>
+        <v>87130.644633660195</v>
       </c>
       <c r="V35">
         <f t="shared" ref="V35:V47" si="15">R35-S35</f>
@@ -4379,11 +4292,11 @@
       </c>
       <c r="W35" s="123">
         <f t="shared" ref="W35:W47" si="16">F35-G35</f>
-        <v>492585.19214512868</v>
+        <v>490691.91071640974</v>
       </c>
       <c r="X35" s="123">
         <f t="shared" ref="X35:X47" si="17">W35+V35-U35</f>
-        <v>412320.71045166266</v>
+        <v>410758.75327296951</v>
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.2">
@@ -4391,18 +4304,18 @@
         <v>2054</v>
       </c>
       <c r="B36">
-        <v>12.242066967108601</v>
-      </c>
-      <c r="C36" s="1">
-        <v>4.2750596700000001</v>
+        <v>36.879446374576901</v>
+      </c>
+      <c r="C36">
+        <v>28.9408028785755</v>
       </c>
       <c r="D36">
         <f t="shared" si="9"/>
-        <v>7.9670072971086006</v>
+        <v>7.9386434960014007</v>
       </c>
       <c r="F36" s="4">
         <f t="shared" si="10"/>
-        <v>531664.95362704725</v>
+        <v>529772.14263316011</v>
       </c>
       <c r="G36">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4442,12 +4355,9 @@
         <f t="shared" si="13"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T36">
-        <v>29</v>
-      </c>
       <c r="U36" s="123">
         <f t="shared" si="14"/>
-        <v>87461.968953314572</v>
+        <v>87130.727029384332</v>
       </c>
       <c r="V36">
         <f t="shared" si="15"/>
@@ -4455,11 +4365,11 @@
       </c>
       <c r="W36" s="123">
         <f t="shared" si="16"/>
-        <v>492585.19254300621</v>
+        <v>490692.38154911908</v>
       </c>
       <c r="X36" s="123">
         <f t="shared" si="17"/>
-        <v>412320.71077991161</v>
+        <v>410759.14170995471</v>
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.2">
@@ -4467,18 +4377,18 @@
         <v>2055</v>
       </c>
       <c r="B37">
-        <v>12.242066423542999</v>
-      </c>
-      <c r="C37" s="1">
-        <v>4.2750591199999999</v>
+        <v>36.879445822446499</v>
+      </c>
+      <c r="C37">
+        <v>28.940795680964701</v>
       </c>
       <c r="D37">
         <f t="shared" si="9"/>
-        <v>7.9670073035429994</v>
+        <v>7.9386501414817978</v>
       </c>
       <c r="F37" s="4">
         <f t="shared" si="10"/>
-        <v>531664.9540564362</v>
+        <v>529772.58610821865</v>
       </c>
       <c r="G37">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4518,12 +4428,9 @@
         <f t="shared" si="13"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T37">
-        <v>30</v>
-      </c>
       <c r="U37" s="123">
         <f t="shared" si="14"/>
-        <v>87461.96902845765</v>
+        <v>87130.80463751957</v>
       </c>
       <c r="V37">
         <f t="shared" si="15"/>
@@ -4531,11 +4438,11 @@
       </c>
       <c r="W37" s="123">
         <f t="shared" si="16"/>
-        <v>492585.19297239516</v>
+        <v>490692.82502417761</v>
       </c>
       <c r="X37" s="123">
         <f t="shared" si="17"/>
-        <v>412320.71113415749</v>
+        <v>410759.50757687801</v>
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.2">
@@ -4543,18 +4450,18 @@
         <v>2056</v>
       </c>
       <c r="B38">
-        <v>12.2420658902518</v>
-      </c>
-      <c r="C38" s="1">
-        <v>4.2750585799999996</v>
+        <v>36.8794452807523</v>
+      </c>
+      <c r="C38">
+        <v>28.9407888186919</v>
       </c>
       <c r="D38">
         <f t="shared" si="9"/>
-        <v>7.9670073102518</v>
+        <v>7.9386564620604005</v>
       </c>
       <c r="F38" s="4">
         <f t="shared" si="10"/>
-        <v>531664.95450413681</v>
+        <v>529773.0079014973</v>
       </c>
       <c r="G38">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4594,12 +4501,9 @@
         <f t="shared" si="13"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T38">
-        <v>31</v>
-      </c>
       <c r="U38" s="123">
         <f t="shared" si="14"/>
-        <v>87461.969106805249</v>
+        <v>87130.878451343335</v>
       </c>
       <c r="V38">
         <f t="shared" si="15"/>
@@ -4607,11 +4511,11 @@
       </c>
       <c r="W38" s="123">
         <f t="shared" si="16"/>
-        <v>492585.19342009578</v>
+        <v>490693.24681745627</v>
       </c>
       <c r="X38" s="123">
         <f t="shared" si="17"/>
-        <v>412320.71150351048</v>
+        <v>410759.85555633291</v>
       </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.2">
@@ -4619,18 +4523,18 @@
         <v>2057</v>
       </c>
       <c r="B39">
-        <v>12.242065367040601</v>
-      </c>
-      <c r="C39" s="1">
-        <v>4.2750580500000002</v>
+        <v>36.8794447492971</v>
+      </c>
+      <c r="C39">
+        <v>28.940782229720401</v>
       </c>
       <c r="D39">
         <f t="shared" si="9"/>
-        <v>7.9670073170406006</v>
+        <v>7.9386625195766989</v>
       </c>
       <c r="F39" s="4">
         <f t="shared" si="10"/>
-        <v>531664.95495717612</v>
+        <v>529773.41213975183</v>
       </c>
       <c r="G39">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4670,12 +4574,9 @@
         <f t="shared" si="13"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T39">
-        <v>32</v>
-      </c>
       <c r="U39" s="123">
         <f t="shared" si="14"/>
-        <v>87461.969186087124</v>
+        <v>87130.949193037886</v>
       </c>
       <c r="V39">
         <f t="shared" si="15"/>
@@ -4683,11 +4584,11 @@
       </c>
       <c r="W39" s="123">
         <f t="shared" si="16"/>
-        <v>492585.19387313508</v>
+        <v>490693.6510557108</v>
       </c>
       <c r="X39" s="123">
         <f t="shared" si="17"/>
-        <v>412320.71187726792</v>
+        <v>410760.18905289291</v>
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.2">
@@ -4695,18 +4596,18 @@
         <v>2058</v>
       </c>
       <c r="B40">
-        <v>12.2420648537191</v>
-      </c>
-      <c r="C40" s="1">
-        <v>4.2750575299999998</v>
+        <v>36.879444227887198</v>
+      </c>
+      <c r="C40">
+        <v>28.940775868752901</v>
       </c>
       <c r="D40">
         <f t="shared" si="9"/>
-        <v>7.9670073237191001</v>
+        <v>7.9386683591342972</v>
       </c>
       <c r="F40" s="4">
         <f t="shared" si="10"/>
-        <v>531664.95540285471</v>
+        <v>529773.80183289549</v>
       </c>
       <c r="G40">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4746,12 +4647,9 @@
         <f t="shared" si="13"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T40">
-        <v>33</v>
-      </c>
       <c r="U40" s="123">
         <f t="shared" si="14"/>
-        <v>87461.969264080879</v>
+        <v>87131.017389338027</v>
       </c>
       <c r="V40">
         <f t="shared" si="15"/>
@@ -4759,11 +4657,11 @@
       </c>
       <c r="W40" s="123">
         <f t="shared" si="16"/>
-        <v>492585.19431881368</v>
+        <v>490694.04074885446</v>
       </c>
       <c r="X40" s="123">
         <f t="shared" si="17"/>
-        <v>412320.7122449528</v>
+        <v>410760.51054973644</v>
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.2">
@@ -4771,18 +4669,18 @@
         <v>2059</v>
       </c>
       <c r="B41">
-        <v>12.242064350100099</v>
-      </c>
-      <c r="C41" s="1">
-        <v>4.2750570200000002</v>
+        <v>36.879443716332901</v>
+      </c>
+      <c r="C41">
+        <v>28.940769702564602</v>
       </c>
       <c r="D41">
         <f t="shared" si="9"/>
-        <v>7.967007330100099</v>
+        <v>7.9386740137682992</v>
       </c>
       <c r="F41" s="4">
         <f t="shared" si="10"/>
-        <v>531664.95582867996</v>
+        <v>529774.17918547115</v>
       </c>
       <c r="G41">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4822,12 +4720,9 @@
         <f t="shared" si="13"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T41">
-        <v>34</v>
-      </c>
       <c r="U41" s="123">
         <f t="shared" si="14"/>
-        <v>87461.969338600305</v>
+        <v>87131.083426038764</v>
       </c>
       <c r="V41">
         <f t="shared" si="15"/>
@@ -4835,11 +4730,11 @@
       </c>
       <c r="W41" s="123">
         <f t="shared" si="16"/>
-        <v>492585.19474463892</v>
+        <v>490694.41810143011</v>
       </c>
       <c r="X41" s="123">
         <f t="shared" si="17"/>
-        <v>412320.71259625861</v>
+        <v>410760.82186561136</v>
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.2">
@@ -4847,18 +4742,18 @@
         <v>2060</v>
       </c>
       <c r="B42">
-        <v>12.242063856000399</v>
-      </c>
-      <c r="C42" s="1">
-        <v>4.2750565199999997</v>
+        <v>36.879443214447797</v>
+      </c>
+      <c r="C42">
+        <v>28.9407637066397</v>
       </c>
       <c r="D42">
         <f t="shared" si="9"/>
-        <v>7.9670073360003997</v>
+        <v>7.9386795078080965</v>
       </c>
       <c r="F42" s="4">
         <f t="shared" si="10"/>
-        <v>531664.95622242661</v>
+        <v>529774.54582106031</v>
       </c>
       <c r="G42">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4898,12 +4793,9 @@
         <f t="shared" si="13"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T42">
-        <v>35</v>
-      </c>
       <c r="U42" s="123">
         <f t="shared" si="14"/>
-        <v>87461.969407505967</v>
+        <v>87131.147587266867</v>
       </c>
       <c r="V42">
         <f t="shared" si="15"/>
@@ -4911,11 +4803,11 @@
       </c>
       <c r="W42" s="123">
         <f t="shared" si="16"/>
-        <v>492585.19513838558</v>
+        <v>490694.78473701928</v>
       </c>
       <c r="X42" s="123">
         <f t="shared" si="17"/>
-        <v>412320.71292109962</v>
+        <v>410761.12433997239</v>
       </c>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.2">
@@ -4923,18 +4815,18 @@
         <v>2061</v>
       </c>
       <c r="B43">
-        <v>12.24206337124</v>
-      </c>
-      <c r="C43" s="1">
-        <v>4.27505603</v>
+        <v>36.879442722049099</v>
+      </c>
+      <c r="C43">
+        <v>28.940757862748701</v>
       </c>
       <c r="D43">
         <f t="shared" si="9"/>
-        <v>7.9670073412400004</v>
+        <v>7.9386848593003982</v>
       </c>
       <c r="F43" s="4">
         <f t="shared" si="10"/>
-        <v>531664.95657208271</v>
+        <v>529774.90294397983</v>
       </c>
       <c r="G43">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -4974,12 +4866,9 @@
         <f t="shared" si="13"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T43">
-        <v>36</v>
-      </c>
       <c r="U43" s="123">
         <f t="shared" si="14"/>
-        <v>87461.969468695781</v>
+        <v>87131.210083777783</v>
       </c>
       <c r="V43">
         <f t="shared" si="15"/>
@@ -4987,11 +4876,11 @@
       </c>
       <c r="W43" s="123">
         <f t="shared" si="16"/>
-        <v>492585.19548804167</v>
+        <v>490695.1418599388</v>
       </c>
       <c r="X43" s="123">
         <f t="shared" si="17"/>
-        <v>412320.71320956585</v>
+        <v>410761.418966381</v>
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.2">
@@ -4999,18 +4888,18 @@
         <v>2062</v>
       </c>
       <c r="B44">
-        <v>12.2420628956424</v>
-      </c>
-      <c r="C44" s="1">
-        <v>4.2750555500000003</v>
+        <v>36.879442238957601</v>
+      </c>
+      <c r="C44">
+        <v>28.9407521572018</v>
       </c>
       <c r="D44">
         <f t="shared" si="9"/>
-        <v>7.9670073456423998</v>
+        <v>7.9386900817558015</v>
       </c>
       <c r="F44" s="4">
         <f t="shared" si="10"/>
-        <v>531664.95686586946</v>
+        <v>529775.25145583716</v>
       </c>
       <c r="G44">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -5050,12 +4939,9 @@
         <f t="shared" si="13"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T44">
-        <v>37</v>
-      </c>
       <c r="U44" s="123">
         <f t="shared" si="14"/>
-        <v>87461.969520108469</v>
+        <v>87131.271073352807</v>
       </c>
       <c r="V44">
         <f t="shared" si="15"/>
@@ -5063,11 +4949,11 @@
       </c>
       <c r="W44" s="123">
         <f t="shared" si="16"/>
-        <v>492585.19578182843</v>
+        <v>490695.49037179613</v>
       </c>
       <c r="X44" s="123">
         <f t="shared" si="17"/>
-        <v>412320.71345193993</v>
+        <v>410761.70648866333</v>
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.2">
@@ -5075,18 +4961,18 @@
         <v>2063</v>
       </c>
       <c r="B45">
-        <v>12.2420624290344</v>
-      </c>
-      <c r="C45" s="1">
-        <v>4.2750550699999996</v>
+        <v>36.879441764997402</v>
+      </c>
+      <c r="C45">
+        <v>28.940746579591</v>
       </c>
       <c r="D45">
         <f t="shared" si="9"/>
-        <v>7.9670073590344002</v>
+        <v>7.9386951854064023</v>
       </c>
       <c r="F45" s="4">
         <f t="shared" si="10"/>
-        <v>531664.9577595623</v>
+        <v>529775.59203945391</v>
       </c>
       <c r="G45">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -5126,12 +5012,9 @@
         <f t="shared" si="13"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T45">
-        <v>38</v>
-      </c>
       <c r="U45" s="123">
         <f t="shared" si="14"/>
-        <v>87461.969676504712</v>
+        <v>87131.330675485748</v>
       </c>
       <c r="V45">
         <f t="shared" si="15"/>
@@ -5139,11 +5022,11 @@
       </c>
       <c r="W45" s="123">
         <f t="shared" si="16"/>
-        <v>492585.19667552126</v>
+        <v>490695.83095541288</v>
       </c>
       <c r="X45" s="123">
         <f t="shared" si="17"/>
-        <v>412320.71418923652</v>
+        <v>410761.98747014708</v>
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.2">
@@ -5151,18 +5034,18 @@
         <v>2064</v>
       </c>
       <c r="B46">
-        <v>12.242061971246001</v>
-      </c>
-      <c r="C46" s="1">
-        <v>4.2750546099999998</v>
+        <v>36.879441299995797</v>
+      </c>
+      <c r="C46">
+        <v>28.940741121882802</v>
       </c>
       <c r="D46">
         <f t="shared" si="9"/>
-        <v>7.9670073612460008</v>
+        <v>7.9387001781129953</v>
       </c>
       <c r="F46" s="4">
         <f t="shared" si="10"/>
-        <v>531664.95790714968</v>
+        <v>529775.92521940719</v>
       </c>
       <c r="G46">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -5202,12 +5085,9 @@
         <f t="shared" si="13"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T46">
-        <v>39</v>
-      </c>
       <c r="U46" s="123">
         <f t="shared" si="14"/>
-        <v>87461.969702332499</v>
+        <v>87131.388981977565</v>
       </c>
       <c r="V46">
         <f t="shared" si="15"/>
@@ -5215,11 +5095,11 @@
       </c>
       <c r="W46" s="123">
         <f t="shared" si="16"/>
-        <v>492585.19682310865</v>
+        <v>490696.16413536615</v>
       </c>
       <c r="X46" s="123">
         <f t="shared" si="17"/>
-        <v>412320.71431099612</v>
+        <v>410762.26234360854</v>
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.2">
@@ -5227,18 +5107,18 @@
         <v>2065</v>
       </c>
       <c r="B47">
-        <v>12.2420615221106</v>
-      </c>
-      <c r="C47" s="1">
-        <v>4.2750541599999998</v>
+        <v>36.879440843783499</v>
+      </c>
+      <c r="C47">
+        <v>28.940735777765202</v>
       </c>
       <c r="D47">
         <f t="shared" si="9"/>
-        <v>7.9670073621105999</v>
+        <v>7.9387050660182972</v>
       </c>
       <c r="F47" s="4">
         <f t="shared" si="10"/>
-        <v>531664.95796484745</v>
+        <v>529776.25140562095</v>
       </c>
       <c r="G47">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
@@ -5278,12 +5158,9 @@
         <f t="shared" si="13"/>
         <v>7261.0188199999993</v>
       </c>
-      <c r="T47">
-        <v>40</v>
-      </c>
       <c r="U47" s="123">
         <f t="shared" si="14"/>
-        <v>87461.969712429607</v>
+        <v>87131.446064564981</v>
       </c>
       <c r="V47">
         <f t="shared" si="15"/>
@@ -5291,11 +5168,11 @@
       </c>
       <c r="W47" s="123">
         <f t="shared" si="16"/>
-        <v>492585.19688080641</v>
+        <v>490696.49032157991</v>
       </c>
       <c r="X47" s="123">
         <f t="shared" si="17"/>
-        <v>412320.71435859677</v>
+        <v>410762.53144723491</v>
       </c>
     </row>
     <row r="49" spans="24:24" x14ac:dyDescent="0.2">
